--- a/generated/spreadsheet/verbose/reserved-matters-reserved-matters-verbose.xlsx
+++ b/generated/spreadsheet/verbose/reserved-matters-reserved-matters-verbose.xlsx
@@ -427,16 +427,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -1024,7 +1024,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>reserved-matters</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3408,12 +3408,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3432,36 +3432,28 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>related-application</t>
+          <t>reserved-matters</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Related application</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Reserved matters[]</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3490,12 +3482,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3504,7 +3496,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3538,12 +3530,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3552,54 +3544,46 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-application</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related application</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>geometry</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3608,17 +3592,17 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>A polygon or multipolygon boundary</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>multipolygon</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3627,49 +3611,41 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-application</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related application</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>site-address</t>
+          <t>eia-application</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>EIA application</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Text representation of an address or site</t>
+          <t>Whether the related application was an Environmental Impact Assessment application</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3683,49 +3659,41 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-application</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related application</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>site-address</t>
+          <t>environmental-statement-submitted</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Environmental statement submitted</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Postcode for a contact address or site</t>
+          <t>Whether an Environmental Statement was submitted with the related application</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3739,54 +3707,38 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>site-address</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Proposal started</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3795,49 +3747,33 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>site-address</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>usrns</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>USRNs[]</t>
-        </is>
-      </c>
+          <t>Proposal start date</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3851,46 +3787,38 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>easting</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3899,41 +3827,33 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>northing</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Northing</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3943,8 +3863,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -3962,12 +3890,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3976,17 +3904,17 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4010,79 +3938,95 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>site-address</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4091,38 +4035,54 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>site-address</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4131,28 +4091,44 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>site-address</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4171,27 +4147,27 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4200,17 +4176,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4219,27 +4195,27 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4248,17 +4224,17 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4267,27 +4243,27 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4296,54 +4272,46 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Supporting information</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>supporting-info</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Any additional information which will help with the planning application</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>replacement-drawings</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Replacement drawings[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>old-drawing-reference</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Old drawing reference</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4352,60 +4320,60 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Reference of the old drawing being replaced</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Any additional information which will help with the planning application</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>replacement-drawings</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Replacement drawings[]</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>new-drawing-reference</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>New drawing reference</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Reference for the new drawing that replaces the old drawing</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4419,44 +4387,500 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Any additional information which will help with the planning application</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>replacement-drawings</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Replacement drawings[]</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>A textual reason</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>contact-reference</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Supporting information</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>supporting-info</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Drawings approved as part of the original decision and drawings submitted with the reserved matters application</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>approved-drawings</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Approved drawings[]</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Name or title of the approved drawing</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Drawings approved as part of the original decision and drawings submitted with the reserved matters application</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>approved-drawings</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Approved drawings[]</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Reference number of the approved drawing</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Drawings approved as part of the original decision and drawings submitted with the reserved matters application</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>submitted-drawing-references</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Submitted drawing references[]</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Reference numbers of drawings submitted with the application for approval</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Drawings approved as part of the original decision and drawings submitted with the reserved matters application</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>approved-drawings-document</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Approved drawings schedule</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Drawings approved as part of the original decision and drawings submitted with the reserved matters application</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>submitted-drawings-document</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Submitted drawings schedule</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Drawings approved as part of the original decision and drawings submitted with the reserved matters application</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Reasons for any changes to the original drawings</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -4464,32 +4888,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="B67:B75"/>
     <mergeCell ref="A37:A43"/>
     <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A82:A87"/>
     <mergeCell ref="A44"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B60:B68"/>
-    <mergeCell ref="A69:A74"/>
+    <mergeCell ref="A56:A66"/>
     <mergeCell ref="B51:B55"/>
-    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="B82:B87"/>
     <mergeCell ref="B24:B32"/>
     <mergeCell ref="A33:A36"/>
     <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B75:B77"/>
     <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B69:B74"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="B33:B36"/>
-    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A67:A75"/>
     <mergeCell ref="A24:A32"/>
     <mergeCell ref="B44"/>
     <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B56:B66"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A60:A68"/>
     <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B76:B81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
